--- a/output/vmu1_site_only/materials_vmu1_site_remaining.xlsx
+++ b/output/vmu1_site_only/materials_vmu1_site_remaining.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L157"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#1</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4598,19 +4598,19 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F84" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G84" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H84" t="n">
         <v>1100</v>
       </c>
       <c r="I84" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=1/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=1/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#2</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4648,19 +4648,19 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F85" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G85" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H85" t="n">
         <v>1100</v>
       </c>
       <c r="I85" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=2/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=2/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#3</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4698,19 +4698,19 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F86" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G86" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H86" t="n">
         <v>1100</v>
       </c>
       <c r="I86" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=3/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=3/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#4</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4748,19 +4748,19 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F87" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G87" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H87" t="n">
         <v>1100</v>
       </c>
       <c r="I87" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=4/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=4/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#5</t>
+          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4798,19 +4798,19 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="F88" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="G88" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H88" t="n">
         <v>1100</v>
       </c>
       <c r="I88" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=5/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=5/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#6</t>
+          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4848,10 +4848,10 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="F89" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G89" t="n">
         <v>4000</v>
@@ -4860,7 +4860,7 @@
         <v>1100</v>
       </c>
       <c r="I89" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=6/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=6/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#7</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4898,19 +4898,19 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F90" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G90" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H90" t="n">
         <v>1100</v>
       </c>
       <c r="I90" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=7/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=7/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#8</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#8</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4948,19 +4948,19 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F91" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G91" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H91" t="n">
         <v>1100</v>
       </c>
       <c r="I91" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=8/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=8/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#9</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#9</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4998,19 +4998,19 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F92" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G92" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H92" t="n">
         <v>1100</v>
       </c>
       <c r="I92" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=9/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=9/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#10</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5048,19 +5048,19 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F93" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G93" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H93" t="n">
         <v>1100</v>
       </c>
       <c r="I93" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=10/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=10/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#11</t>
+          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5098,19 +5098,19 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="F94" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="G94" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H94" t="n">
         <v>1100</v>
       </c>
       <c r="I94" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=11/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=11/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#12</t>
+          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5148,10 +5148,10 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="F95" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G95" t="n">
         <v>4000</v>
@@ -5160,7 +5160,7 @@
         <v>1100</v>
       </c>
       <c r="I95" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=12/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=12/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#13</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#13</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5198,19 +5198,19 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F96" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G96" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H96" t="n">
         <v>1100</v>
       </c>
       <c r="I96" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=13/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=13/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#14</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#14</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5248,19 +5248,19 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F97" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G97" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H97" t="n">
         <v>1100</v>
       </c>
       <c r="I97" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=14/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=14/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#15</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5298,19 +5298,19 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F98" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G98" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H98" t="n">
         <v>1100</v>
       </c>
       <c r="I98" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=15/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=15/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#16</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#16</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5348,19 +5348,19 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F99" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G99" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H99" t="n">
         <v>1100</v>
       </c>
       <c r="I99" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=16/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=16/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#17</t>
+          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#17</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5398,19 +5398,19 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="F100" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="G100" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H100" t="n">
         <v>1100</v>
       </c>
       <c r="I100" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=17/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=17/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#18</t>
+          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#18</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5448,10 +5448,10 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="F101" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G101" t="n">
         <v>4000</v>
@@ -5460,7 +5460,7 @@
         <v>1100</v>
       </c>
       <c r="I101" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=18/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=18/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#19</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#19</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5498,19 +5498,19 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F102" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G102" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H102" t="n">
         <v>1100</v>
       </c>
       <c r="I102" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=19/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=19/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#20</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#20</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5548,19 +5548,19 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F103" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G103" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H103" t="n">
         <v>1100</v>
       </c>
       <c r="I103" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=20/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=20/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#21</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#21</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5598,19 +5598,19 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F104" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G104" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H104" t="n">
         <v>1100</v>
       </c>
       <c r="I104" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=21/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=21/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#22</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#22</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5648,19 +5648,19 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F105" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G105" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H105" t="n">
         <v>1100</v>
       </c>
       <c r="I105" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=22/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=22/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#23</t>
+          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#23</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5698,19 +5698,19 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="F106" t="n">
-        <v>450</v>
+        <v>1340</v>
       </c>
       <c r="G106" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H106" t="n">
         <v>1100</v>
       </c>
       <c r="I106" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=23/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=23/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#24</t>
+          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#24</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5748,10 +5748,10 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="F107" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G107" t="n">
         <v>4000</v>
@@ -5760,7 +5760,7 @@
         <v>1100</v>
       </c>
       <c r="I107" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=24/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=24/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#25</t>
+          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#25</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5798,19 +5798,19 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="F108" t="n">
-        <v>450</v>
+        <v>1280</v>
       </c>
       <c r="G108" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="H108" t="n">
         <v>1100</v>
       </c>
       <c r="I108" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=25/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=25/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#26</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5848,28 +5848,28 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="F109" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G109" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H109" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I109" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=26/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=1/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#27</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5898,28 +5898,28 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="F110" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G110" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H110" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I110" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=27/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=2/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#28</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5948,28 +5948,28 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="F111" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G111" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H111" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I111" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=28/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=3/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#29</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#4</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5998,28 +5998,28 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G112" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H112" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I112" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=29/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=4/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#30</t>
+          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6048,28 +6048,28 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F113" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="G113" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="H113" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I113" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0022</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=30/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=189.0; crate=1/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#31</t>
+          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6098,28 +6098,28 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F114" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="G114" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="H114" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I114" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0022</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=31/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=189.0; crate=2/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#32</t>
+          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6148,2131 +6148,31 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F115" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="G115" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="H115" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I115" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-FST0003</t>
+          <t>SLTO-VMU-0001-FST0022</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=1998.0; crate=32/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=189.0; crate=3/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>S115</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#33</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="n">
-        <v>450</v>
-      </c>
-      <c r="F116" t="n">
-        <v>450</v>
-      </c>
-      <c r="G116" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H116" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I116" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=33/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>S116</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#34</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" t="n">
-        <v>450</v>
-      </c>
-      <c r="F117" t="n">
-        <v>450</v>
-      </c>
-      <c r="G117" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H117" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I117" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=34/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>S117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#35</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" t="n">
-        <v>450</v>
-      </c>
-      <c r="F118" t="n">
-        <v>450</v>
-      </c>
-      <c r="G118" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H118" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I118" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=35/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>S118</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#36</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" t="n">
-        <v>450</v>
-      </c>
-      <c r="F119" t="n">
-        <v>450</v>
-      </c>
-      <c r="G119" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H119" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=36/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>S119</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#37</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>450</v>
-      </c>
-      <c r="F120" t="n">
-        <v>450</v>
-      </c>
-      <c r="G120" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=37/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>S120</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#38</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="n">
-        <v>450</v>
-      </c>
-      <c r="F121" t="n">
-        <v>450</v>
-      </c>
-      <c r="G121" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I121" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=38/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>S121</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#39</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" t="n">
-        <v>450</v>
-      </c>
-      <c r="F122" t="n">
-        <v>450</v>
-      </c>
-      <c r="G122" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H122" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I122" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=39/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>S122</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#40</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" t="n">
-        <v>450</v>
-      </c>
-      <c r="F123" t="n">
-        <v>450</v>
-      </c>
-      <c r="G123" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H123" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I123" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=40/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>S123</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#41</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="n">
-        <v>450</v>
-      </c>
-      <c r="F124" t="n">
-        <v>450</v>
-      </c>
-      <c r="G124" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H124" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I124" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=41/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>S124</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#42</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" t="n">
-        <v>450</v>
-      </c>
-      <c r="F125" t="n">
-        <v>450</v>
-      </c>
-      <c r="G125" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H125" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I125" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=42/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>S125</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#43</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" t="n">
-        <v>450</v>
-      </c>
-      <c r="F126" t="n">
-        <v>450</v>
-      </c>
-      <c r="G126" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H126" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I126" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=43/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>S126</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#44</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>450</v>
-      </c>
-      <c r="F127" t="n">
-        <v>450</v>
-      </c>
-      <c r="G127" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H127" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I127" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=44/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>S127</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#45</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>450</v>
-      </c>
-      <c r="F128" t="n">
-        <v>450</v>
-      </c>
-      <c r="G128" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H128" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I128" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=45/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>S128</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#46</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" t="n">
-        <v>450</v>
-      </c>
-      <c r="F129" t="n">
-        <v>450</v>
-      </c>
-      <c r="G129" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H129" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I129" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=46/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>S129</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#47</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" t="n">
-        <v>450</v>
-      </c>
-      <c r="F130" t="n">
-        <v>450</v>
-      </c>
-      <c r="G130" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H130" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I130" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=47/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>S130</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#48</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>450</v>
-      </c>
-      <c r="F131" t="n">
-        <v>450</v>
-      </c>
-      <c r="G131" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H131" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I131" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=48/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>S131</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#49</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" t="n">
-        <v>450</v>
-      </c>
-      <c r="F132" t="n">
-        <v>450</v>
-      </c>
-      <c r="G132" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H132" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I132" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=49/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>S132</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#50</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>450</v>
-      </c>
-      <c r="F133" t="n">
-        <v>450</v>
-      </c>
-      <c r="G133" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H133" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I133" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=50/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>S133</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#51</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="n">
-        <v>450</v>
-      </c>
-      <c r="F134" t="n">
-        <v>450</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H134" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I134" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=51/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>S134</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#52</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>450</v>
-      </c>
-      <c r="F135" t="n">
-        <v>450</v>
-      </c>
-      <c r="G135" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H135" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I135" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=52/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>S135</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#53</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="n">
-        <v>450</v>
-      </c>
-      <c r="F136" t="n">
-        <v>450</v>
-      </c>
-      <c r="G136" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H136" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I136" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=53/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>S136</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#54</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>450</v>
-      </c>
-      <c r="F137" t="n">
-        <v>450</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H137" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I137" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=54/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>S137</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#55</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>450</v>
-      </c>
-      <c r="F138" t="n">
-        <v>450</v>
-      </c>
-      <c r="G138" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H138" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I138" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=55/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>S138</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#56</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>450</v>
-      </c>
-      <c r="F139" t="n">
-        <v>450</v>
-      </c>
-      <c r="G139" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I139" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=56/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>S139</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#57</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>450</v>
-      </c>
-      <c r="F140" t="n">
-        <v>450</v>
-      </c>
-      <c r="G140" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=57/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>S140</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#58</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>450</v>
-      </c>
-      <c r="F141" t="n">
-        <v>450</v>
-      </c>
-      <c r="G141" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H141" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I141" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=58/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>S141</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#59</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>450</v>
-      </c>
-      <c r="F142" t="n">
-        <v>450</v>
-      </c>
-      <c r="G142" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H142" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I142" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=59/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>S142</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#60</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>450</v>
-      </c>
-      <c r="F143" t="n">
-        <v>450</v>
-      </c>
-      <c r="G143" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H143" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I143" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=60/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>S143</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#61</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>450</v>
-      </c>
-      <c r="F144" t="n">
-        <v>450</v>
-      </c>
-      <c r="G144" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H144" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=61/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>S144</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#62</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>450</v>
-      </c>
-      <c r="F145" t="n">
-        <v>450</v>
-      </c>
-      <c r="G145" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H145" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I145" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=62/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>S145</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#63</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>450</v>
-      </c>
-      <c r="F146" t="n">
-        <v>450</v>
-      </c>
-      <c r="G146" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H146" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I146" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=63/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>S146</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#64</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>450</v>
-      </c>
-      <c r="F147" t="n">
-        <v>450</v>
-      </c>
-      <c r="G147" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H147" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I147" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=64/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>S147</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#65</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>450</v>
-      </c>
-      <c r="F148" t="n">
-        <v>450</v>
-      </c>
-      <c r="G148" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H148" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=65/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>S148</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#66</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>450</v>
-      </c>
-      <c r="F149" t="n">
-        <v>450</v>
-      </c>
-      <c r="G149" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H149" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I149" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=66/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>S149</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>铁件架×30件/架 raw=1998 | SLTO-VMU-0001-FST0003#67</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>450</v>
-      </c>
-      <c r="F150" t="n">
-        <v>450</v>
-      </c>
-      <c r="G150" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H150" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I150" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=67/67; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>S150</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>45</v>
-      </c>
-      <c r="F151" t="n">
-        <v>45</v>
-      </c>
-      <c r="G151" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H151" t="n">
-        <v>800</v>
-      </c>
-      <c r="I151" t="n">
-        <v>600</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=1/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>S151</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#2</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>45</v>
-      </c>
-      <c r="F152" t="n">
-        <v>45</v>
-      </c>
-      <c r="G152" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H152" t="n">
-        <v>800</v>
-      </c>
-      <c r="I152" t="n">
-        <v>600</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=2/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>S152</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#3</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>45</v>
-      </c>
-      <c r="F153" t="n">
-        <v>45</v>
-      </c>
-      <c r="G153" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H153" t="n">
-        <v>800</v>
-      </c>
-      <c r="I153" t="n">
-        <v>600</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=3/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>S153</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#4</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>45</v>
-      </c>
-      <c r="F154" t="n">
-        <v>45</v>
-      </c>
-      <c r="G154" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H154" t="n">
-        <v>800</v>
-      </c>
-      <c r="I154" t="n">
-        <v>600</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=4/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>S154</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#1</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>150</v>
-      </c>
-      <c r="F155" t="n">
-        <v>150</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H155" t="n">
-        <v>800</v>
-      </c>
-      <c r="I155" t="n">
-        <v>600</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=1/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>S155</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#2</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>150</v>
-      </c>
-      <c r="F156" t="n">
-        <v>150</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H156" t="n">
-        <v>800</v>
-      </c>
-      <c r="I156" t="n">
-        <v>600</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=2/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>S156</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#3</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>150</v>
-      </c>
-      <c r="F157" t="n">
-        <v>150</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H157" t="n">
-        <v>800</v>
-      </c>
-      <c r="I157" t="n">
-        <v>600</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=3/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
         <is>
           <t>工地</t>
         </is>

--- a/output/vmu1_site_only/materials_vmu1_site_remaining.xlsx
+++ b/output/vmu1_site_only/materials_vmu1_site_remaining.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#1</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,19 +498,19 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H2" t="n">
         <v>600</v>
       </c>
-      <c r="H2" t="n">
-        <v>400</v>
-      </c>
       <c r="I2" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=1/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=1/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#2</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -548,19 +548,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H3" t="n">
         <v>600</v>
       </c>
-      <c r="H3" t="n">
-        <v>400</v>
-      </c>
       <c r="I3" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=2/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=2/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#3</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,19 +598,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
+        <v>800</v>
+      </c>
+      <c r="H4" t="n">
         <v>600</v>
       </c>
-      <c r="H4" t="n">
-        <v>400</v>
-      </c>
       <c r="I4" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=3/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=3/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#4</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -648,19 +648,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
+        <v>800</v>
+      </c>
+      <c r="H5" t="n">
         <v>600</v>
       </c>
-      <c r="H5" t="n">
-        <v>400</v>
-      </c>
       <c r="I5" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=4/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=4/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#5</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -698,19 +698,19 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
+        <v>800</v>
+      </c>
+      <c r="H6" t="n">
         <v>600</v>
       </c>
-      <c r="H6" t="n">
-        <v>400</v>
-      </c>
       <c r="I6" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=5/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=5/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#6</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -748,19 +748,19 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
+        <v>800</v>
+      </c>
+      <c r="H7" t="n">
         <v>600</v>
       </c>
-      <c r="H7" t="n">
-        <v>400</v>
-      </c>
       <c r="I7" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=6/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=6/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#7</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -798,19 +798,19 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
+        <v>800</v>
+      </c>
+      <c r="H8" t="n">
         <v>600</v>
       </c>
-      <c r="H8" t="n">
-        <v>400</v>
-      </c>
       <c r="I8" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=7/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=7/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#8</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -848,19 +848,19 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
+        <v>800</v>
+      </c>
+      <c r="H9" t="n">
         <v>600</v>
       </c>
-      <c r="H9" t="n">
-        <v>400</v>
-      </c>
       <c r="I9" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=8/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=8/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#9</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -898,19 +898,19 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
+        <v>800</v>
+      </c>
+      <c r="H10" t="n">
         <v>600</v>
       </c>
-      <c r="H10" t="n">
-        <v>400</v>
-      </c>
       <c r="I10" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=9/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=9/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#10</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -948,19 +948,19 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
+        <v>800</v>
+      </c>
+      <c r="H11" t="n">
         <v>600</v>
       </c>
-      <c r="H11" t="n">
-        <v>400</v>
-      </c>
       <c r="I11" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=10/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=10/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#11</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -998,19 +998,19 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
+        <v>800</v>
+      </c>
+      <c r="H12" t="n">
         <v>600</v>
       </c>
-      <c r="H12" t="n">
-        <v>400</v>
-      </c>
       <c r="I12" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=11/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=11/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#12</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1048,19 +1048,19 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
+        <v>800</v>
+      </c>
+      <c r="H13" t="n">
         <v>600</v>
       </c>
-      <c r="H13" t="n">
-        <v>400</v>
-      </c>
       <c r="I13" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=12/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=12/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#13</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1098,19 +1098,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
+        <v>800</v>
+      </c>
+      <c r="H14" t="n">
         <v>600</v>
       </c>
-      <c r="H14" t="n">
-        <v>400</v>
-      </c>
       <c r="I14" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=13/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=13/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#14</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1148,19 +1148,19 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
+        <v>800</v>
+      </c>
+      <c r="H15" t="n">
         <v>600</v>
       </c>
-      <c r="H15" t="n">
-        <v>400</v>
-      </c>
       <c r="I15" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=14/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=14/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#15</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1198,19 +1198,19 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
+        <v>800</v>
+      </c>
+      <c r="H16" t="n">
         <v>600</v>
       </c>
-      <c r="H16" t="n">
-        <v>400</v>
-      </c>
       <c r="I16" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=15/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=15/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#16</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1248,19 +1248,19 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
+        <v>800</v>
+      </c>
+      <c r="H17" t="n">
         <v>600</v>
       </c>
-      <c r="H17" t="n">
-        <v>400</v>
-      </c>
       <c r="I17" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=16/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=16/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#17</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1298,19 +1298,19 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
+        <v>800</v>
+      </c>
+      <c r="H18" t="n">
         <v>600</v>
       </c>
-      <c r="H18" t="n">
-        <v>400</v>
-      </c>
       <c r="I18" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=17/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=17/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#18</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1348,19 +1348,19 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
+        <v>800</v>
+      </c>
+      <c r="H19" t="n">
         <v>600</v>
       </c>
-      <c r="H19" t="n">
-        <v>400</v>
-      </c>
       <c r="I19" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=18/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=18/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#19</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1398,19 +1398,19 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
+        <v>800</v>
+      </c>
+      <c r="H20" t="n">
         <v>600</v>
       </c>
-      <c r="H20" t="n">
-        <v>400</v>
-      </c>
       <c r="I20" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=19/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=19/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#20</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1448,19 +1448,19 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
+        <v>800</v>
+      </c>
+      <c r="H21" t="n">
         <v>600</v>
       </c>
-      <c r="H21" t="n">
-        <v>400</v>
-      </c>
       <c r="I21" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=20/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=20/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#21</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1498,19 +1498,19 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
+        <v>800</v>
+      </c>
+      <c r="H22" t="n">
         <v>600</v>
       </c>
-      <c r="H22" t="n">
-        <v>400</v>
-      </c>
       <c r="I22" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=21/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=21/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#22</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0007#22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1548,19 +1548,19 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H23" t="n">
         <v>600</v>
       </c>
-      <c r="H23" t="n">
-        <v>400</v>
-      </c>
       <c r="I23" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=22/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=8762.0; crate=22/22; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#23</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0022#1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1598,28 +1598,28 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
+        <v>800</v>
+      </c>
+      <c r="H24" t="n">
         <v>600</v>
       </c>
-      <c r="H24" t="n">
-        <v>400</v>
-      </c>
       <c r="I24" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BBF0022</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=23/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=1/2; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#24</t>
+          <t>五金箱当量×400件/箱 | SLTO-VMU-0001-BBF0022#2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1648,28 +1648,28 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G25" t="n">
+        <v>800</v>
+      </c>
+      <c r="H25" t="n">
         <v>600</v>
       </c>
-      <c r="H25" t="n">
-        <v>400</v>
-      </c>
       <c r="I25" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BBF0022</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=24/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=2/2; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1686,40 +1686,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#25</t>
+          <t>胶条垫块箱×60/箱 | SLTO-VMU-0001-BGK0015#1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>19—胶条、垫块、胶皮</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
+        <v>800</v>
+      </c>
+      <c r="H26" t="n">
         <v>600</v>
       </c>
-      <c r="H26" t="n">
-        <v>400</v>
-      </c>
       <c r="I26" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BGK0015</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=25/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=110.0; crate=1/2; arr=0.0; pend=110.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1736,40 +1736,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#26</t>
+          <t>胶条垫块箱×60/箱 | SLTO-VMU-0001-BGK0015#2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>19—胶条、垫块、胶皮</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
+        <v>800</v>
+      </c>
+      <c r="H27" t="n">
         <v>600</v>
       </c>
-      <c r="H27" t="n">
-        <v>400</v>
-      </c>
       <c r="I27" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BGK0015</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=26/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=110.0; crate=2/2; arr=0.0; pend=110.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1786,40 +1786,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#27</t>
+          <t>胶条垫块箱×60/箱 | SLTO-VMU-0001-BGK0055#1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>19—胶条、垫块、胶皮</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
+        <v>800</v>
+      </c>
+      <c r="H28" t="n">
         <v>600</v>
       </c>
-      <c r="H28" t="n">
-        <v>400</v>
-      </c>
       <c r="I28" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BGK0055</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=27/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=100.0; crate=1/2; arr=0.0; pend=100.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1836,40 +1836,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#28</t>
+          <t>胶条垫块箱×60/箱 | SLTO-VMU-0001-BGK0055#2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>19—胶条、垫块、胶皮</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
+        <v>800</v>
+      </c>
+      <c r="H29" t="n">
         <v>600</v>
       </c>
-      <c r="H29" t="n">
-        <v>400</v>
-      </c>
       <c r="I29" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BGK0055</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=28/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=100.0; crate=2/2; arr=0.0; pend=100.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1886,40 +1886,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#29</t>
+          <t>木板架×30/架 | SLTO-VMU-0001-BOM0016#1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="G30" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H30" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I30" t="n">
         <v>400</v>
       </c>
-      <c r="I30" t="n">
-        <v>350</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0016</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=29/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=80.0; crate=1/3; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1936,40 +1936,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#30</t>
+          <t>木板架×30/架 | SLTO-VMU-0001-BOM0016#2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="G31" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I31" t="n">
         <v>400</v>
       </c>
-      <c r="I31" t="n">
-        <v>350</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0016</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=30/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=80.0; crate=2/3; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1986,40 +1986,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#31</t>
+          <t>木板架×30/架 | SLTO-VMU-0001-BOM0016#3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>540</v>
       </c>
       <c r="G32" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H32" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I32" t="n">
         <v>400</v>
       </c>
-      <c r="I32" t="n">
-        <v>350</v>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0016</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=31/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=80.0; crate=3/3; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2036,40 +2036,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#32</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G33" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H33" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I33" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=32/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=1/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2086,40 +2086,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#33</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F34" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G34" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H34" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I34" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=33/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=2/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2136,40 +2136,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#34</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G35" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H35" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I35" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=34/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=3/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2186,40 +2186,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#35</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G36" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H36" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I36" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=35/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=4/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2236,40 +2236,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#36</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G37" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H37" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I37" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=36/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=5/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2286,40 +2286,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#37</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G38" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H38" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I38" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=37/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=6/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2336,40 +2336,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#38</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F39" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G39" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H39" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I39" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=38/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=7/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2386,40 +2386,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#39</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G40" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H40" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I40" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=39/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=8/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2436,40 +2436,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#40</t>
+          <t>瓦楞板架×80/架 | SLTO-VMU-0001-BOM0019#9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>28—杂项配件</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>640</v>
       </c>
       <c r="G41" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="H41" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I41" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-BOM0019</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=40/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=702.0; crate=9/9; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2486,40 +2486,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#41</t>
+          <t>铝板架×40片/架 | SLTO-VMU-0001-FAC0011#1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>11—铝板</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="G42" t="n">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="H42" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I42" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-FAC0011</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=41/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=128.0; crate=1/3; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2536,40 +2536,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#42</t>
+          <t>铝板架×40片/架 | SLTO-VMU-0001-FAC0011#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>11—铝板</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="G43" t="n">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="H43" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I43" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-FAC0011</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=42/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=128.0; crate=2/3; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2586,40 +2586,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#43</t>
+          <t>铝板架×40片/架 | SLTO-VMU-0001-FAC0011#3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>11—铝板</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="F44" t="n">
-        <v>25</v>
+        <v>720</v>
       </c>
       <c r="G44" t="n">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="H44" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I44" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-FAC0011</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=43/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=128.0; crate=3/3; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2636,40 +2636,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0007#44</t>
+          <t>不锈钢箱 | SLTO-VMU-0001-FSS0005#1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>14—不锈钢</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H45" t="n">
+        <v>800</v>
+      </c>
+      <c r="I45" t="n">
         <v>600</v>
       </c>
-      <c r="H45" t="n">
-        <v>400</v>
-      </c>
-      <c r="I45" t="n">
-        <v>350</v>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0007</t>
+          <t>SLTO-VMU-0001-FSS0005</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=8762.0; crate=44/44; arr=0.0; pend=8762.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=2.0; crate=1/2; arr=2.0; pend=0.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2686,40 +2686,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0022#1</t>
+          <t>不锈钢箱 | SLTO-VMU-0001-FSS0005#2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>14—不锈钢</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H46" t="n">
+        <v>800</v>
+      </c>
+      <c r="I46" t="n">
         <v>600</v>
       </c>
-      <c r="H46" t="n">
-        <v>400</v>
-      </c>
-      <c r="I46" t="n">
-        <v>350</v>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0022</t>
+          <t>SLTO-VMU-0001-FSS0005</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=1/4; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=2.0; crate=2/2; arr=2.0; pend=0.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2736,40 +2736,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0022#2</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="F47" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="G47" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="H47" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I47" t="n">
-        <v>350</v>
+        <v>1750</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0022</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=2/4; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=1/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2786,40 +2786,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0022#3</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="G48" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="H48" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I48" t="n">
-        <v>350</v>
+        <v>1750</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0022</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=3/4; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=2/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2836,40 +2836,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>五金箱当量×200件/箱 | SLTO-VMU-0001-BBF0022#4</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>23—紧固件/螺丝</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>1580</v>
       </c>
       <c r="G49" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="H49" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I49" t="n">
-        <v>350</v>
+        <v>1750</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BBF0022</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=4/4; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=3/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2886,40 +2886,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>胶条垫块箱×40/箱 | SLTO-VMU-0001-BGK0015#1</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>19—胶条、垫块、胶皮</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="G50" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="H50" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I50" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BGK0015</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=110.0; crate=1/3; arr=0.0; pend=110.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=4/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2936,40 +2936,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>胶条垫块箱×40/箱 | SLTO-VMU-0001-BGK0015#2</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>19—胶条、垫块、胶皮</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="G51" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="H51" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I51" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BGK0015</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=110.0; crate=2/3; arr=0.0; pend=110.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=5/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -2986,40 +2986,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>胶条垫块箱×40/箱 | SLTO-VMU-0001-BGK0015#3</t>
+          <t>2米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>19—胶条、垫块、胶皮</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>30</v>
+        <v>1640</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>1640</v>
       </c>
       <c r="G52" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="H52" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I52" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BGK0015</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=110.0; crate=3/3; arr=0.0; pend=110.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=6/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3036,40 +3036,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>胶条垫块箱×40/箱 | SLTO-VMU-0001-BGK0055#1</t>
+          <t>4米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>19—胶条、垫块、胶皮</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>30</v>
+        <v>1750</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>1750</v>
       </c>
       <c r="G53" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="H53" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I53" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BGK0055</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=100.0; crate=1/2; arr=0.0; pend=100.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=7/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3086,40 +3086,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>胶条垫块箱×40/箱 | SLTO-VMU-0001-BGK0055#2</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>19—胶条、垫块、胶皮</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>1580</v>
       </c>
       <c r="G54" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="H54" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I54" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BGK0055</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=100.0; crate=2/2; arr=0.0; pend=100.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=8/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3136,40 +3136,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>木板架×20/架 | SLTO-VMU-0001-BOM0016#1</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="F55" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="G55" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H55" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I55" t="n">
-        <v>400</v>
+        <v>1750</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0016</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=80.0; crate=1/4; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=9/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3186,40 +3186,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>木板架×20/架 | SLTO-VMU-0001-BOM0016#2</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="F56" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="G56" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H56" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I56" t="n">
-        <v>400</v>
+        <v>1750</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0016</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=80.0; crate=2/4; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=10/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3236,40 +3236,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>木板架×20/架 | SLTO-VMU-0001-BOM0016#3</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="F57" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="G57" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H57" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I57" t="n">
-        <v>400</v>
+        <v>1750</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0016</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=80.0; crate=3/4; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=11/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3286,40 +3286,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>木板架×20/架 | SLTO-VMU-0001-BOM0016#4</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="F58" t="n">
-        <v>360</v>
+        <v>1580</v>
       </c>
       <c r="G58" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H58" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I58" t="n">
-        <v>400</v>
+        <v>1750</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0016</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=80.0; crate=4/4; arr=0.0; pend=80.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=12/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3336,40 +3336,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#1</t>
+          <t>2米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#13</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>320</v>
+        <v>1640</v>
       </c>
       <c r="F59" t="n">
-        <v>320</v>
+        <v>1640</v>
       </c>
       <c r="G59" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H59" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I59" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=1/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=13/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3386,40 +3386,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#2</t>
+          <t>4米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>320</v>
+        <v>1750</v>
       </c>
       <c r="F60" t="n">
-        <v>320</v>
+        <v>1750</v>
       </c>
       <c r="G60" t="n">
-        <v>2400</v>
+        <v>4000</v>
       </c>
       <c r="H60" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I60" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=2/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=14/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3436,40 +3436,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#3</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="F61" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="G61" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H61" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I61" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=3/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=15/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3486,40 +3486,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#4</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="F62" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="G62" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H62" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I62" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=4/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=16/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3536,40 +3536,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#5</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="F63" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="G63" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H63" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I63" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=5/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=17/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3586,40 +3586,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#6</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="F64" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="G64" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H64" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I64" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=6/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=18/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3636,40 +3636,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#7</t>
+          <t>1.1米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="F65" t="n">
-        <v>320</v>
+        <v>1580</v>
       </c>
       <c r="G65" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H65" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I65" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=7/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=19/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3686,40 +3686,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#8</t>
+          <t>2米铁件架×100件/架 raw=1998 | SLTO-VMU-0001-FST0003#20</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>320</v>
+        <v>1640</v>
       </c>
       <c r="F66" t="n">
-        <v>320</v>
+        <v>1640</v>
       </c>
       <c r="G66" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H66" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I66" t="n">
-        <v>600</v>
+        <v>1750</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0003</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=8/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=1998.0; crate=20/20; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3736,40 +3736,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#9</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="F67" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="G67" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H67" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I67" t="n">
         <v>600</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=9/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=1/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3786,40 +3786,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#10</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="F68" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="G68" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H68" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I68" t="n">
         <v>600</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=10/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=2/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3836,40 +3836,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#11</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="F69" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H69" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I69" t="n">
         <v>600</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=11/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=3/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3886,40 +3886,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#12</t>
+          <t>吊具 | SLTO-VMU-0001-FST0017#4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="F70" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="G70" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H70" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I70" t="n">
         <v>600</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0017</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=12/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=4.0; crate=4/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -3936,40 +3936,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#13</t>
+          <t>钢垫片箱×90/箱 | SLTO-VMU-0001-FST0022#1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="F71" t="n">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="G71" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="H71" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I71" t="n">
         <v>600</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0022</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=13/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=189.0; crate=1/2; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -3986,2193 +3986,43 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#14</t>
+          <t>钢垫片箱×90/箱 | SLTO-VMU-0001-FST0022#2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>28—杂项配件</t>
+          <t>13—铁件</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="F72" t="n">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="G72" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="H72" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I72" t="n">
         <v>600</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
+          <t>SLTO-VMU-0001-FST0022</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>dest=工地; raw_qty=702.0; crate=14/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
+          <t>dest=工地; raw_qty=189.0; crate=2/2; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>S072</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#15</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>28—杂项配件</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>320</v>
-      </c>
-      <c r="F73" t="n">
-        <v>320</v>
-      </c>
-      <c r="G73" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H73" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I73" t="n">
-        <v>600</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=702.0; crate=15/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>S073</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#16</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>28—杂项配件</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>320</v>
-      </c>
-      <c r="F74" t="n">
-        <v>320</v>
-      </c>
-      <c r="G74" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H74" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I74" t="n">
-        <v>600</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=702.0; crate=16/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>S074</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>28—杂项配件</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="n">
-        <v>320</v>
-      </c>
-      <c r="F75" t="n">
-        <v>320</v>
-      </c>
-      <c r="G75" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H75" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I75" t="n">
-        <v>600</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=702.0; crate=17/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>S075</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>瓦楞板架×40/架 | SLTO-VMU-0001-BOM0019#18</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>28—杂项配件</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>320</v>
-      </c>
-      <c r="F76" t="n">
-        <v>320</v>
-      </c>
-      <c r="G76" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H76" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I76" t="n">
-        <v>600</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-BOM0019</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=702.0; crate=18/18; arr=0.0; pend=702.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>S076</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>铝板架×25片/架 | SLTO-VMU-0001-FAC0011#1</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>11—铝板</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>450</v>
-      </c>
-      <c r="F77" t="n">
-        <v>450</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H77" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I77" t="n">
-        <v>800</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FAC0011</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=128.0; crate=1/5; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>S077</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>铝板架×25片/架 | SLTO-VMU-0001-FAC0011#2</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>11—铝板</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>450</v>
-      </c>
-      <c r="F78" t="n">
-        <v>450</v>
-      </c>
-      <c r="G78" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H78" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I78" t="n">
-        <v>800</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FAC0011</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=128.0; crate=2/5; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>S078</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>铝板架×25片/架 | SLTO-VMU-0001-FAC0011#3</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>11—铝板</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>450</v>
-      </c>
-      <c r="F79" t="n">
-        <v>450</v>
-      </c>
-      <c r="G79" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H79" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I79" t="n">
-        <v>800</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FAC0011</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=128.0; crate=3/5; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>S079</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>铝板架×25片/架 | SLTO-VMU-0001-FAC0011#4</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>11—铝板</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>450</v>
-      </c>
-      <c r="F80" t="n">
-        <v>450</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I80" t="n">
-        <v>800</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FAC0011</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=128.0; crate=4/5; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>S080</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>铝板架×25片/架 | SLTO-VMU-0001-FAC0011#5</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>11—铝板</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>450</v>
-      </c>
-      <c r="F81" t="n">
-        <v>450</v>
-      </c>
-      <c r="G81" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H81" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I81" t="n">
-        <v>800</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FAC0011</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=128.0; crate=5/5; arr=0.0; pend=128.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>S081</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>不锈钢箱 | SLTO-VMU-0001-FSS0005#1</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>14—不锈钢</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>4</v>
-      </c>
-      <c r="F82" t="n">
-        <v>4</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H82" t="n">
-        <v>800</v>
-      </c>
-      <c r="I82" t="n">
-        <v>600</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FSS0005</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=2.0; crate=1/2; arr=2.0; pend=0.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>S082</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>不锈钢箱 | SLTO-VMU-0001-FSS0005#2</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>14—不锈钢</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>4</v>
-      </c>
-      <c r="F83" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H83" t="n">
-        <v>800</v>
-      </c>
-      <c r="I83" t="n">
-        <v>600</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FSS0005</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=2.0; crate=2/2; arr=2.0; pend=0.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>S083</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=1/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>S084</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#2</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=2/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>S085</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#3</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F86" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H86" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=3/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>S086</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#4</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H87" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=4/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>S087</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#5</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G88" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=5/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>S088</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#6</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G89" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=6/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>S089</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#7</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=7/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>S090</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#8</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H91" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=8/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>S091</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#9</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=9/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>S092</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#10</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H93" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=10/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>S093</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#11</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F94" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H94" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=11/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>S094</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#12</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G95" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=12/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>S095</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#13</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=13/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>S096</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#14</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H97" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=14/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>S097</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#15</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H98" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I98" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=15/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>S098</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#16</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H99" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=16/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>S099</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#17</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G100" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H100" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=17/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>S100</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#18</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G101" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H101" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=18/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>S101</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#19</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=19/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>S102</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#20</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H103" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I103" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=20/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>S103</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#21</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H104" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I104" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=21/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>S104</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#22</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H105" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I105" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=22/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>S105</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#23</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G106" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H106" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I106" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=23/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>S106</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>4米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#24</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G107" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H107" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=24/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>S107</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1.1米铁件架×80件/架 raw=1998 | SLTO-VMU-0001-FST0003#25</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1280</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H108" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0003</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=1998.0; crate=25/25; arr=0.0; pend=1998.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>S108</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#1</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="n">
-        <v>45</v>
-      </c>
-      <c r="F109" t="n">
-        <v>45</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H109" t="n">
-        <v>800</v>
-      </c>
-      <c r="I109" t="n">
-        <v>600</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=1/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>S109</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#2</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>45</v>
-      </c>
-      <c r="F110" t="n">
-        <v>45</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H110" t="n">
-        <v>800</v>
-      </c>
-      <c r="I110" t="n">
-        <v>600</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=2/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>S110</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#3</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" t="n">
-        <v>45</v>
-      </c>
-      <c r="F111" t="n">
-        <v>45</v>
-      </c>
-      <c r="G111" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H111" t="n">
-        <v>800</v>
-      </c>
-      <c r="I111" t="n">
-        <v>600</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=3/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>S111</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>吊具 | SLTO-VMU-0001-FST0017#4</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" t="n">
-        <v>45</v>
-      </c>
-      <c r="F112" t="n">
-        <v>45</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H112" t="n">
-        <v>800</v>
-      </c>
-      <c r="I112" t="n">
-        <v>600</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0017</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=4.0; crate=4/4; arr=0.0; pend=4.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>S112</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#1</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" t="n">
-        <v>150</v>
-      </c>
-      <c r="F113" t="n">
-        <v>150</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H113" t="n">
-        <v>800</v>
-      </c>
-      <c r="I113" t="n">
-        <v>600</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=1/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>S113</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#2</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" t="n">
-        <v>150</v>
-      </c>
-      <c r="F114" t="n">
-        <v>150</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H114" t="n">
-        <v>800</v>
-      </c>
-      <c r="I114" t="n">
-        <v>600</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=2/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>工地</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>S114</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>钢垫片箱×60/箱 | SLTO-VMU-0001-FST0022#3</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>13—铁件</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" t="n">
-        <v>150</v>
-      </c>
-      <c r="F115" t="n">
-        <v>150</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H115" t="n">
-        <v>800</v>
-      </c>
-      <c r="I115" t="n">
-        <v>600</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>SLTO-VMU-0001-FST0022</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>dest=工地; raw_qty=189.0; crate=3/3; arr=0.0; pend=189.0; dims=crate_equiv_est</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
         <is>
           <t>工地</t>
         </is>
